--- a/manuscript_package/tables/table02_performance_across_validation_regimes.xlsx
+++ b/manuscript_package/tables/table02_performance_across_validation_regimes.xlsx
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +27,21 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E8FB"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +56,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -411,455 +430,368 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>n_splits</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>r2_mean</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>r2_sd</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>rmse_mean</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>rmse_sd</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>mae_mean</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>mae_sd</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Validation regime</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>N splits</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Mean R2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>SD R2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Mean RMSE</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>SD RMSE</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Mean MAE</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>SD MAE</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>group_aut</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>elastic_net</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Grouped by study</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D2" t="n">
-        <v>-0.904982491767686</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1.443712998855472</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1.673805531810816</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.67104956639349</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.8503492518047491</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.7770557841291408</v>
+      <c r="D2" s="3" t="n">
+        <v>-0.905</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>1.444</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>1.674</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>1.671</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>0.777</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>group_aut</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>lightgbm</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Grouped by study</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>LGBM</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D3" t="n">
-        <v>-9.75481220984031</v>
-      </c>
-      <c r="E3" t="n">
-        <v>14.15685888405377</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1.905727425448214</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.460267793120895</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.967099225810415</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.7351692828588715</v>
+      <c r="D3" s="3" t="n">
+        <v>-9.755000000000001</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>14.157</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>1.906</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>0.735</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>group_aut</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>mlp_regressor</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Grouped by study</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D4" t="n">
-        <v>-21744.53809353333</v>
-      </c>
-      <c r="E4" t="n">
-        <v>48263.88493418768</v>
-      </c>
-      <c r="F4" t="n">
-        <v>19.48066101940038</v>
-      </c>
-      <c r="G4" t="n">
-        <v>22.37959344916794</v>
-      </c>
-      <c r="H4" t="n">
-        <v>15.52724165553027</v>
-      </c>
-      <c r="I4" t="n">
-        <v>19.25685496465657</v>
+      <c r="D4" s="3" t="n">
+        <v>-21744.538</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>48263.885</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>19.481</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>22.38</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>15.527</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>19.257</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>group_exp</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>lightgbm</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Grouped by experiment</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>LGBM</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D5" t="n">
-        <v>0.7248646976187476</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.2026569683660244</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.9686451675105228</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.3865931621193039</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.3834757204100092</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.164123142569866</v>
+      <c r="D5" s="3" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0.203</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>0.164</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>group_exp</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>mlp_regressor</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Grouped by experiment</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D6" t="n">
-        <v>0.703321343305128</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.1198689438994553</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1.096952480304577</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.5373124609015354</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.4675681701599998</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.2485192738727613</v>
+      <c r="D6" s="3" t="n">
+        <v>0.703</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>1.097</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0.537</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0.249</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>group_exp</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>elastic_net</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Grouped by experiment</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D7" t="n">
-        <v>0.0164050730624396</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.09651134814892411</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2.027713026136947</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.8791238647512568</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.8460187629853027</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.3125571942405796</v>
+      <c r="D7" s="3" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>2.028</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>0.313</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>leave_one_study_out</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>elastic_net</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>23</v>
-      </c>
-      <c r="D8" t="n">
-        <v>-1879.083340716945</v>
-      </c>
-      <c r="E8" t="n">
-        <v>7460.54800823419</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1.291760678681451</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2.162696930961643</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.067138796496988</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.721028711434223</v>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Random CV</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0.223</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>0.038</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>leave_one_study_out</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lightgbm</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>23</v>
-      </c>
-      <c r="D9" t="n">
-        <v>-157.1440082660946</v>
-      </c>
-      <c r="E9" t="n">
-        <v>485.003558999751</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.408192754525223</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.107893103693478</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.132947076136178</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.687873913487181</v>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Random CV</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>LGBM</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>0.065</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>leave_one_study_out</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mlp_regressor</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>23</v>
-      </c>
-      <c r="D10" t="n">
-        <v>-206691.5481316932</v>
-      </c>
-      <c r="E10" t="n">
-        <v>941502.5838050708</v>
-      </c>
-      <c r="F10" t="n">
-        <v>4.200490417397792</v>
-      </c>
-      <c r="G10" t="n">
-        <v>11.03146781540554</v>
-      </c>
-      <c r="H10" t="n">
-        <v>3.710877482735986</v>
-      </c>
-      <c r="I10" t="n">
-        <v>11.00667713403313</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>random_cv</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>mlp_regressor</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Random CV</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="D11" t="n">
-        <v>0.9124249412297316</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.0390631456385801</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.6183173727026338</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.1177471212150087</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.2227703838431752</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.0384385359194226</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>random_cv</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>lightgbm</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>15</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.8705052412229396</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.0699669192727734</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.7623678086629639</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.2240678860695487</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.2602242454909437</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.06498990786490939</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>random_cv</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>elastic_net</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>15</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.0126663419970575</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.0334389432053105</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2.146477482220385</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.2930766061286242</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.8386320478157606</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.1186436443283613</v>
+      <c r="D10" s="3" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>2.146</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>0.119</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>